--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/phi-4/simple/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/phi-4/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="D3">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G3">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H3">
         <v>426</v>
